--- a/data/sample_chart.xlsx
+++ b/data/sample_chart.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m\月d\日"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Noto Sans CJK JP"/>
       <charset val="1"/>
@@ -40,11 +40,6 @@
     <font>
       <name val="Arial"/>
       <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Noto Sans CJK JP"/>
-      <family val="2"/>
       <sz val="10"/>
     </font>
     <font>
@@ -94,7 +89,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,7 +99,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -118,545 +113,76 @@
   </cellStyles>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFB3B3B3"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFD320"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF420E"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF004586"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>Sheet1!$A$2</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>最大値</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="004586"/>
-            </a:solidFill>
-            <a:ln w="28800">
-              <a:solidFill>
-                <a:srgbClr val="004586"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="square"/>
-            <size val="8"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="004586"/>
-              </a:solidFill>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <txPr>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="r"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>Sheet1!$B$1:$F$1</f>
-              <strCache>
-                <ptCount val="5"/>
-                <pt idx="0">
-                  <v>4月12日</v>
-                </pt>
-                <pt idx="1">
-                  <v>4月13日</v>
-                </pt>
-                <pt idx="2">
-                  <v>4月14日</v>
-                </pt>
-                <pt idx="3">
-                  <v>4月15日</v>
-                </pt>
-                <pt idx="4">
-                  <v>4月16日</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>Sheet1!$B$2:$F$2</f>
-              <numCache>
-                <formatCode>General</formatCode>
-                <ptCount val="5"/>
-                <pt idx="0">
-                  <v>600</v>
-                </pt>
-                <pt idx="1">
-                  <v>450</v>
-                </pt>
-                <pt idx="2">
-                  <v>550</v>
-                </pt>
-                <pt idx="3">
-                  <v>650</v>
-                </pt>
-                <pt idx="4">
-                  <v>500</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>Sheet1!$A$3</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>最小値</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="ff420e"/>
-            </a:solidFill>
-            <a:ln w="28800">
-              <a:solidFill>
-                <a:srgbClr val="ff420e"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="diamond"/>
-            <size val="8"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="ff420e"/>
-              </a:solidFill>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <txPr>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="r"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>Sheet1!$B$1:$F$1</f>
-              <strCache>
-                <ptCount val="5"/>
-                <pt idx="0">
-                  <v>4月12日</v>
-                </pt>
-                <pt idx="1">
-                  <v>4月13日</v>
-                </pt>
-                <pt idx="2">
-                  <v>4月14日</v>
-                </pt>
-                <pt idx="3">
-                  <v>4月15日</v>
-                </pt>
-                <pt idx="4">
-                  <v>4月16日</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>Sheet1!$B$3:$F$3</f>
-              <numCache>
-                <formatCode>General</formatCode>
-                <ptCount val="5"/>
-                <pt idx="0">
-                  <v>550</v>
-                </pt>
-                <pt idx="1">
-                  <v>500</v>
-                </pt>
-                <pt idx="2">
-                  <v>750</v>
-                </pt>
-                <pt idx="3">
-                  <v>650</v>
-                </pt>
-                <pt idx="4">
-                  <v>450</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>Sheet1!$A$4</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>中央値</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="ffd320"/>
-            </a:solidFill>
-            <a:ln w="28800">
-              <a:solidFill>
-                <a:srgbClr val="ffd320"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="triangle"/>
-            <size val="8"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="ffd320"/>
-              </a:solidFill>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <txPr>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="r"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>Sheet1!$B$1:$F$1</f>
-              <strCache>
-                <ptCount val="5"/>
-                <pt idx="0">
-                  <v>4月12日</v>
-                </pt>
-                <pt idx="1">
-                  <v>4月13日</v>
-                </pt>
-                <pt idx="2">
-                  <v>4月14日</v>
-                </pt>
-                <pt idx="3">
-                  <v>4月15日</v>
-                </pt>
-                <pt idx="4">
-                  <v>4月16日</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>Sheet1!$B$4:$F$4</f>
-              <numCache>
-                <formatCode>General</formatCode>
-                <ptCount val="5"/>
-                <pt idx="0">
-                  <v>600</v>
-                </pt>
-                <pt idx="1">
-                  <v>750</v>
-                </pt>
-                <pt idx="2">
-                  <v>600</v>
-                </pt>
-                <pt idx="3">
-                  <v>750</v>
-                </pt>
-                <pt idx="4">
-                  <v>550</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <hiLowLines>
-          <spPr>
-            <a:ln w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </hiLowLines>
-        <marker val="1"/>
-        <axId val="82400985"/>
-        <axId val="29418205"/>
-      </lineChart>
-      <catAx>
-        <axId val="82400985"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="m\月d\日" sourceLinked="0"/>
-        <majorTickMark val="out"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln w="0">
-            <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="29418205"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="29418205"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln w="0">
-              <a:solidFill>
-                <a:srgbClr val="b3b3b3"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="out"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln w="0">
-            <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="82400985"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="midCat"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-              <a:latin typeface="Arial"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill>
-      <a:srgbClr val="ffffff"/>
-    </a:solidFill>
-    <a:ln w="0">
-      <a:noFill/>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <plotArea>
@@ -683,12 +209,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Sheet1'!$B$1:$F$1</f>
+              <f>'Sheet1'!$C$2:$G$2</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Sheet1'!$B$2:$F$2</f>
+              <f>'Sheet1'!$C$3:$G$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -714,12 +240,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Sheet1'!$B$1:$F$1</f>
+              <f>'Sheet1'!$C$2:$G$2</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Sheet1'!$B$3:$F$3</f>
+              <f>'Sheet1'!$C$4:$G$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -745,12 +271,146 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Sheet1'!$B$1:$F$1</f>
+              <f>'Sheet1'!$C$2:$G$2</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Sheet1'!$B$4:$F$4</f>
+              <f>'Sheet1'!$C$5:$G$5</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>標準偏差</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="auto"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Sheet1'!$C$16:$G$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Sheet1'!$C$17:$G$17</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>中央値</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="auto"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Sheet1'!$C$16:$G$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Sheet1'!$C$18:$G$18</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>分散</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="auto"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Sheet1'!$C$16:$G$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Sheet1'!$C$19:$G$19</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -792,19 +452,14 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
+  <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>8</col>
       <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>28440</rowOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <to>
-      <col>7</col>
-      <colOff>29160</colOff>
-      <row>27</row>
-      <rowOff>16200</rowOff>
-    </to>
+    <ext cx="4320000" cy="2160000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -818,15 +473,15 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </twoCellAnchor>
+  </oneCellAnchor>
   <oneCellAnchor>
     <from>
       <col>8</col>
       <colOff>0</colOff>
-      <row>0</row>
+      <row>15</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5760000" cy="2880000"/>
+    <ext cx="4320000" cy="2160000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1133,107 +788,189 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A2:G19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
-    <row r="1" ht="15.65" customHeight="1" s="5">
-      <c r="B1" s="6" t="n">
+    <row r="2" ht="15.65" customHeight="1" s="5">
+      <c r="C2" s="6" t="n">
         <v>45028</v>
       </c>
-      <c r="C1" s="6">
-        <f>B1+1</f>
+      <c r="D2" s="6">
+        <f>C2+1</f>
         <v/>
       </c>
-      <c r="D1" s="6">
-        <f>C1+1</f>
+      <c r="E2" s="6">
+        <f>D2+1</f>
         <v/>
       </c>
-      <c r="E1" s="6">
-        <f>D1+1</f>
+      <c r="F2" s="6">
+        <f>E2+1</f>
         <v/>
       </c>
-      <c r="F1" s="6">
-        <f>E1+1</f>
+      <c r="G2" s="6">
+        <f>F2+1</f>
         <v/>
       </c>
     </row>
-    <row r="2" ht="12.8" customHeight="1" s="5">
-      <c r="A2" s="7" t="inlineStr">
+    <row r="3" ht="12.8" customHeight="1" s="5">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>最大値</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n">
+      <c r="C3" s="7" t="n">
         <v>600</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="D3" s="7" t="n">
         <v>450</v>
       </c>
-      <c r="D2" s="7" t="n">
+      <c r="E3" s="7" t="n">
         <v>550</v>
       </c>
-      <c r="E2" s="7" t="n">
+      <c r="F3" s="7" t="n">
         <v>650</v>
       </c>
-      <c r="F2" s="7" t="n">
+      <c r="G3" s="7" t="n">
         <v>500</v>
       </c>
     </row>
-    <row r="3" ht="12.8" customHeight="1" s="5">
-      <c r="A3" s="7" t="inlineStr">
+    <row r="4" ht="12.8" customHeight="1" s="5">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>最小値</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
+      <c r="C4" s="7" t="n">
         <v>550</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="D4" s="7" t="n">
         <v>500</v>
-      </c>
-      <c r="D3" s="7" t="n">
-        <v>750</v>
-      </c>
-      <c r="E3" s="7" t="n">
-        <v>650</v>
-      </c>
-      <c r="F3" s="7" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="4" ht="12.8" customHeight="1" s="5">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>中央値</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>600</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>750</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>600</v>
       </c>
       <c r="E4" s="7" t="n">
         <v>750</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>550</v>
+        <v>650</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="5" ht="12.8" customHeight="1" s="5">
       <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>中央値</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>600</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>750</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>600</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>750</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>550</v>
+      </c>
     </row>
     <row r="6" ht="12.8" customHeight="1" s="5">
       <c r="A6" s="7" t="n"/>
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>
+    </row>
+    <row r="16" ht="15.65" customHeight="1" s="5">
+      <c r="C16" s="6" t="n">
+        <v>45028</v>
+      </c>
+      <c r="D16" s="6">
+        <f>C16+1</f>
+        <v/>
+      </c>
+      <c r="E16" s="6">
+        <f>D16+1</f>
+        <v/>
+      </c>
+      <c r="F16" s="6">
+        <f>E16+1</f>
+        <v/>
+      </c>
+      <c r="G16" s="6">
+        <f>F16+1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="12.8" customHeight="1" s="5">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>標準偏差</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>450</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>650</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>600</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>450</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="18" ht="12.8" customHeight="1" s="5">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>中央値</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>450</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>550</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>650</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="19" ht="12.8" customHeight="1" s="5">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>分散</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>750</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>650</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>450</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>550</v>
+      </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
